--- a/outputs/evaluation/architecture/design/v3/CF_M05/run_2/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v3/CF_M05/run_2/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6341</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6471</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9371</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5714</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8963</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1254,13 +1265,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1281,7 +1290,6 @@
       <c r="D3" t="n">
         <v>0.8094</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1302,7 +1310,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_21</t>
@@ -1313,7 +1320,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1332,7 +1338,6 @@
           <t>CF_M05_AU06, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU24</t>
@@ -1383,14 +1388,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Client(Frontend)</t>
@@ -1416,13 +1418,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1468,13 +1468,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Contract Layer (DTO/Mappers)</t>
@@ -1499,13 +1497,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU20</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1526,7 +1522,6 @@
       <c r="D6" t="n">
         <v>0.86</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1547,7 +1542,6 @@
           <t>['AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1558,7 +1552,6 @@
           <t>view, viewmodel, model</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1579,7 +1572,6 @@
           <t xml:space="preserve">CF_M05_AU14, CF_M05_AU13, CF_M05_AU15 </t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU27</t>
@@ -1630,14 +1622,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1662,13 +1651,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1709,14 +1696,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
@@ -1741,13 +1725,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1788,14 +1770,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1822,13 +1801,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1869,14 +1846,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1905,13 +1879,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1952,14 +1924,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1988,13 +1957,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2040,13 +2007,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -2072,13 +2037,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2124,13 +2087,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -2154,13 +2115,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2206,13 +2165,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2237,13 +2194,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2264,7 +2219,6 @@
       <c r="D15" t="n">
         <v>0.9514</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2285,7 +2239,6 @@
           <t>['AU_04', 'AU_02']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_25</t>
@@ -2296,7 +2249,6 @@
           <t>viewmodel, server</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2315,7 +2267,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -2371,13 +2322,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2401,13 +2350,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2428,7 +2375,6 @@
       <c r="D17" t="n">
         <v>0.9641999999999999</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2449,7 +2395,6 @@
           <t>['AU_11', 'AU_12', 'AU_13', 'AU_14', 'AU_15']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_22</t>
@@ -2460,7 +2405,6 @@
           <t>leader service, portal service, access control service, communication log service, scheduler service</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2479,7 +2423,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -2535,13 +2478,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2563,14 +2504,11 @@
       <c r="P18" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2616,13 +2554,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>View</t>
@@ -2648,13 +2584,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2700,13 +2634,11 @@
           <t>['AU_25']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2731,13 +2663,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2783,13 +2713,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2815,13 +2743,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2867,13 +2793,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2893,14 +2817,11 @@
       <c r="P22" t="n">
         <v>62</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2946,13 +2867,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2976,13 +2895,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3023,14 +2940,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3049,14 +2963,11 @@
       <c r="P24" t="n">
         <v>56</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3102,13 +3013,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Model</t>
@@ -3134,13 +3043,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3181,14 +3088,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3209,7 +3113,6 @@
       <c r="P26" t="n">
         <v>61</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3220,7 +3123,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3266,13 +3168,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>ViewModel</t>
@@ -3298,13 +3198,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3378,7 +3276,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The data format used is JSON.</t>
@@ -3414,7 +3311,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The provider for this project is Amazon Web Services.</t>
@@ -3445,7 +3341,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, business logic layer, data access layer</t>
@@ -3542,7 +3437,6 @@
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
@@ -3580,7 +3474,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -3619,7 +3512,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -3655,7 +3547,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -3692,7 +3583,6 @@
           <t>Ordering</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3729,7 +3619,6 @@
           <t>GSB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3766,7 +3655,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3799,7 +3687,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client(frontend), amazon eks</t>
@@ -3835,7 +3722,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -3851,7 +3737,6 @@
           <t>AU_25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0.7419</v>
       </c>
@@ -3867,7 +3752,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3908,7 +3792,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -3945,7 +3828,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3981,7 +3863,6 @@
           <t>Kubernetes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>which allows the use of Kubernetes (K8s), a container orchestration platform created by
@@ -4018,7 +3899,6 @@
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
@@ -4055,7 +3935,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
